--- a/output/pdf_financials_xlsx/AORO.xlsx
+++ b/output/pdf_financials_xlsx/AORO.xlsx
@@ -4202,31 +4202,31 @@
         <v>2.014637</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.014637</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.014637</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.103992</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.103992</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.048896</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.048896</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.021137</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.021137</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.021137</v>
       </c>
     </row>
     <row r="93">
@@ -6719,7 +6719,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -7251,7 +7255,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -7673,7 +7681,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -8724,7 +8736,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -9085,7 +9101,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -9590,7 +9610,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -10164,7 +10188,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AORO.xlsx
+++ b/output/pdf_financials_xlsx/AORO.xlsx
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.004767</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.469853</v>
+        <v>-2.47462</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.556601</v>
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.466809</v>
+        <v>-2.471576</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.549185</v>
@@ -1800,37 +1800,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.096233</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.006584</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.167467</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.369017</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.404647</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.012924</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.03825</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.018483</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.009923</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.000887</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.06753000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1880,37 +1880,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.096233</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.006584</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.167467</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.369017</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.404647</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.012924</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.03825</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.018483</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.009923</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.000887</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.06753000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2360,34 +2360,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.106247</v>
+        <v>0.010014</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.006584</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.167467</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.369017</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.404647</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.013996</v>
+        <v>0.001072</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.039543</v>
+        <v>0.001293</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.018483</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.009923</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.599209</v>
+        <v>0.598322</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -5458,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.025867</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
         <v>0</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.025867</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
@@ -6057,7 +6057,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -13859,7 +13859,11 @@
           <t>Principal elements of lease payments</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -17089,7 +17093,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -19824,7 +19828,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -25048,7 +25052,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E273" s="5" t="n">

--- a/output/pdf_financials_xlsx/AORO.xlsx
+++ b/output/pdf_financials_xlsx/AORO.xlsx
@@ -5289,10 +5289,10 @@
         <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>0.539407</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="F120" s="3" t="n">
         <v>0</v>
@@ -14790,7 +14790,11 @@
           <t>Proceeds from issuance of common shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AORO.xlsx
+++ b/output/pdf_financials_xlsx/AORO.xlsx
@@ -649,37 +649,37 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.110734</v>
+        <v>0.308734</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.129186</v>
+        <v>0.209663</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.050371</v>
+        <v>0.137371</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.022843</v>
+        <v>0.256843</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.030012</v>
+        <v>0.246012</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.031834</v>
+        <v>0.247834</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.014411</v>
+        <v>0.230411</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.025816</v>
+        <v>0.241816</v>
       </c>
     </row>
     <row r="8">
@@ -769,16 +769,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>0.237</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>0.246</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.228</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.110734</v>
+        <v>0.308734</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.37921</v>
@@ -4523,13 +4523,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.006705</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.008078999999999999</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.018536</v>
+        <v>-0.000557</v>
       </c>
       <c r="E101" s="3" t="n">
         <v>-0.000211</v>
@@ -4723,13 +4723,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.01937</v>
+        <v>0.012665</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.279038</v>
+        <v>0.270959</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.052701</v>
+        <v>-0.034722</v>
       </c>
       <c r="E106" s="3" t="n">
         <v>0.219436</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.099803</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.016195</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -13792,7 +13792,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -14579,7 +14583,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -14719,7 +14727,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -15492,7 +15504,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -15561,7 +15577,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E138" s="5" t="n">
         <v>-0.006705</v>
       </c>
@@ -16632,7 +16652,11 @@
           <t>Management and director fees (Note 9) $</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -19550,7 +19574,11 @@
           <t>Management and director fees 11</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -20885,7 +20913,11 @@
           <t>Management and director fees 8</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -21875,7 +21907,11 @@
           <t>Management and directors fees (Note 6)</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -22859,7 +22895,11 @@
           <t>Management and directors fees (Note 8)</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -24632,7 +24672,11 @@
           <t>Management and directors fees (Note 14)</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E267" s="5" t="n">
         <v>0.237</v>
       </c>
